--- a/facility_management_forms/010_facility_upgrade_voting_form--facility_management_forms.xlsx
+++ b/facility_management_forms/010_facility_upgrade_voting_form--facility_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page</t>
+          <t>facility_upgrade_voting_form_page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>What type of facility upgrade would you prefer?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>Which location would you prefer for the upgrade?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>How many people would be impacted by the upgrade?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>When would you like the upgrade to happen?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>What time of day would you prefer for the upgrade?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>How would you like to receive updates about the upgrade?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>What benefits do you think the upgrade would bring?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>How do you feel about the upgrade's budget?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>Would you like to provide any additional comments about the upgrade?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>How likely are you to participate in the upgrade?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>What is the expected duration of the upgrade process?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>How would you rate the importance of the upgrade?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>What is your expected outcome of the upgrade?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>Do you expect any challenges with the upgrade?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>Do you expect any positive outcomes with the upgrade?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>Do you think the upgrade is a good idea?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>What is your preferred method of communication for the upgrade?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -916,103 +916,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Facility Upgrade Voting Form</t>
+          <t>Do you have any other suggestions for the upgrade?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>facility_upgrade_voting_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Facility Upgrade Voting Form</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>facility_upgrade_voting_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Facility Upgrade Voting Form</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>facility_upgrade_voting_form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Facility Upgrade Voting Form</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>facility_upgrade_voting_form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Facility Upgrade Voting Form</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1029,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1057,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_2_choices</t>
+          <t>facility_upgrade_voting_form_page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1074,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_2_choices</t>
+          <t>facility_upgrade_voting_form_page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1091,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_3_choices</t>
+          <t>facility_upgrade_voting_form_page_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1108,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_3_choices</t>
+          <t>facility_upgrade_voting_form_page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1125,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_7_choices</t>
+          <t>facility_upgrade_voting_form_page_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1142,7 +1050,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_7_choices</t>
+          <t>facility_upgrade_voting_form_page_6_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1159,7 +1067,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_10_choices</t>
+          <t>facility_upgrade_voting_form_page_8_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_10_choices</t>
+          <t>facility_upgrade_voting_form_page_8_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1193,7 +1101,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_11_choices</t>
+          <t>facility_upgrade_voting_form_page_10_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1210,7 +1118,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_11_choices</t>
+          <t>facility_upgrade_voting_form_page_10_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1227,7 +1135,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_14_choices</t>
+          <t>facility_upgrade_voting_form_page_11_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1244,7 +1152,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_14_choices</t>
+          <t>facility_upgrade_voting_form_page_11_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1261,7 +1169,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_17_choices</t>
+          <t>facility_upgrade_voting_form_page_12_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1278,7 +1186,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_17_choices</t>
+          <t>facility_upgrade_voting_form_page_12_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1295,7 +1203,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_18_choices</t>
+          <t>facility_upgrade_voting_form_page_14_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1312,7 +1220,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_18_choices</t>
+          <t>facility_upgrade_voting_form_page_14_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1329,7 +1237,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_19_choices</t>
+          <t>facility_upgrade_voting_form_page_15_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1346,7 +1254,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_19_choices</t>
+          <t>facility_upgrade_voting_form_page_15_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1363,7 +1271,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_20_choices</t>
+          <t>facility_upgrade_voting_form_page_16_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1380,7 +1288,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>facility_upgrade_voting_form_page_20_choices</t>
+          <t>facility_upgrade_voting_form_page_16_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1389,6 +1297,40 @@
         </is>
       </c>
       <c r="C21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>facility_upgrade_voting_form_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>facility_upgrade_voting_form_page_17_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
